--- a/platform_PiN_output/Haiti___HTI/PiN_results_Haiti___HTI_1021_04PM.xlsx
+++ b/platform_PiN_output/Haiti___HTI/PiN_results_Haiti___HTI_1021_04PM.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN total par admin" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- Non-déplacé" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- Déplacé" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paramètres Utilisés" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PiN -- Retourné" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paramètres Utilisés" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -584,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="3" max="3"/>
@@ -734,7 +735,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1479416</v>
+        <v>1493669</v>
       </c>
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
@@ -744,34 +745,34 @@
         </is>
       </c>
       <c r="I6" s="9" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>1638822</v>
+        <v>1649788</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>38.7</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>1206478</v>
+        <v>1217454</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>3</v>
       </c>
       <c r="N6" s="9" t="n">
-        <v>93090</v>
+        <v>94277</v>
       </c>
       <c r="O6" s="9" t="n">
         <v>5.8</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>179848</v>
+        <v>181938</v>
       </c>
       <c r="Q6" s="9" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="R6" s="9" t="n">
-        <v>1479416</v>
+        <v>1493669</v>
       </c>
       <c r="S6" s="9" t="inlineStr">
         <is>
@@ -779,7 +780,7 @@
         </is>
       </c>
       <c r="T6" s="9" t="n">
-        <v>3118238</v>
+        <v>3143456</v>
       </c>
     </row>
     <row r="7">
@@ -909,41 +910,71 @@
     <row r="9">
       <c r="A9" s="2" t="n"/>
       <c r="B9" s="2" t="n"/>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Filles (5-17 ans)</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Tous les groupes de population</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>729386</v>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Retourné (5-17 ans)</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>14253</v>
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
-      <c r="H9" s="2" t="n"/>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n"/>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Retourné (5-17 ans)</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>10966</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>10976</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N9" s="11" t="n">
+        <v>1187</v>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>2090</v>
+      </c>
+      <c r="Q9" s="11" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="R9" s="11" t="n">
+        <v>14253</v>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>25218</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
       <c r="B10" s="2" t="n"/>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Garcons (5-17 ans)</t>
+          <t>Filles (5-17 ans)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -952,7 +983,7 @@
         </is>
       </c>
       <c r="E10" s="12" t="n">
-        <v>750030</v>
+        <v>736212</v>
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
@@ -973,18 +1004,18 @@
     <row r="11">
       <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="n"/>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Éducation préscolaire (5 ans)</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Garcons (5-17 ans)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Tous les groupes de population</t>
         </is>
       </c>
-      <c r="E11" s="13" t="n">
-        <v>117148</v>
+      <c r="E11" s="12" t="n">
+        <v>757457</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -1007,7 +1038,7 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Enfants en situation de handicap</t>
+          <t>Éducation préscolaire (5 ans)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -1016,7 +1047,7 @@
         </is>
       </c>
       <c r="E12" s="13" t="n">
-        <v>147942</v>
+        <v>118352</v>
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
@@ -1033,6 +1064,38 @@
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Enfants en situation de handicap</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Tous les groupes de population</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>149367</v>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1158,37 +1221,37 @@
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>197698</v>
+        <v>198910</v>
       </c>
       <c r="G6" s="23" t="n">
         <v>39.4</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>77965</v>
+        <v>78443</v>
       </c>
       <c r="I6" s="24" t="n">
         <v>18.3</v>
       </c>
       <c r="J6" s="24" t="n">
-        <v>36198</v>
+        <v>36420</v>
       </c>
       <c r="K6" s="25" t="n">
         <v>8.5</v>
       </c>
       <c r="L6" s="25" t="n">
-        <v>16707</v>
+        <v>16809</v>
       </c>
       <c r="M6" s="26" t="n">
         <v>33.8</v>
       </c>
       <c r="N6" s="26" t="n">
-        <v>66827</v>
+        <v>67237</v>
       </c>
       <c r="O6" s="27" t="n">
         <v>60.6</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>119733</v>
+        <v>120467</v>
       </c>
       <c r="Q6" s="28" t="inlineStr">
         <is>
@@ -1207,37 +1270,37 @@
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>110133</v>
+        <v>110263</v>
       </c>
       <c r="G7" s="23" t="n">
         <v>60.7</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>66822</v>
+        <v>66901</v>
       </c>
       <c r="I7" s="24" t="n">
         <v>16.9</v>
       </c>
       <c r="J7" s="24" t="n">
-        <v>18562</v>
+        <v>18584</v>
       </c>
       <c r="K7" s="25" t="n">
         <v>5.6</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>6187</v>
+        <v>6195</v>
       </c>
       <c r="M7" s="26" t="n">
         <v>16.9</v>
       </c>
       <c r="N7" s="26" t="n">
-        <v>18562</v>
+        <v>18584</v>
       </c>
       <c r="O7" s="27" t="n">
         <v>39.3</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>43311</v>
+        <v>43362</v>
       </c>
       <c r="Q7" s="28" t="inlineStr">
         <is>
@@ -1256,25 +1319,25 @@
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>104220</v>
+        <v>104245</v>
       </c>
       <c r="G8" s="23" t="n">
         <v>29.9</v>
       </c>
       <c r="H8" s="23" t="n">
-        <v>31169</v>
+        <v>31176</v>
       </c>
       <c r="I8" s="24" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="J8" s="24" t="n">
-        <v>69155</v>
+        <v>69172</v>
       </c>
       <c r="K8" s="25" t="n">
         <v>2.8</v>
       </c>
       <c r="L8" s="25" t="n">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="M8" s="26" t="n">
         <v>0.9</v>
@@ -1286,7 +1349,7 @@
         <v>70.09999999999999</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>73051</v>
+        <v>73069</v>
       </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
@@ -1305,37 +1368,37 @@
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>89893</v>
+        <v>89943</v>
       </c>
       <c r="G9" s="23" t="n">
         <v>72.40000000000001</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>65127</v>
+        <v>65163</v>
       </c>
       <c r="I9" s="24" t="n">
         <v>22.4</v>
       </c>
       <c r="J9" s="24" t="n">
-        <v>20180</v>
+        <v>20191</v>
       </c>
       <c r="K9" s="25" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="M9" s="26" t="n">
         <v>3.1</v>
       </c>
       <c r="N9" s="26" t="n">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="O9" s="27" t="n">
         <v>27.6</v>
       </c>
       <c r="P9" s="27" t="n">
-        <v>24766</v>
+        <v>24780</v>
       </c>
       <c r="Q9" s="28" t="inlineStr">
         <is>
@@ -1354,37 +1417,37 @@
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>15236</v>
+        <v>15413</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>46</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>7014</v>
+        <v>7095</v>
       </c>
       <c r="I10" s="24" t="n">
         <v>35.8</v>
       </c>
       <c r="J10" s="24" t="n">
-        <v>5452</v>
+        <v>5516</v>
       </c>
       <c r="K10" s="25" t="n">
         <v>5.4</v>
       </c>
       <c r="L10" s="25" t="n">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="M10" s="26" t="n">
         <v>12.8</v>
       </c>
       <c r="N10" s="26" t="n">
-        <v>1953</v>
+        <v>1976</v>
       </c>
       <c r="O10" s="27" t="n">
         <v>54</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>8222</v>
+        <v>8318</v>
       </c>
       <c r="Q10" s="28" t="inlineStr">
         <is>
@@ -1452,37 +1515,37 @@
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>72364</v>
+        <v>73267</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>43</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>31133</v>
+        <v>31522</v>
       </c>
       <c r="I12" s="24" t="n">
         <v>43</v>
       </c>
       <c r="J12" s="24" t="n">
-        <v>31133</v>
+        <v>31522</v>
       </c>
       <c r="K12" s="25" t="n">
         <v>5.2</v>
       </c>
       <c r="L12" s="25" t="n">
-        <v>3786</v>
+        <v>3834</v>
       </c>
       <c r="M12" s="26" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>6311</v>
+        <v>6390</v>
       </c>
       <c r="O12" s="27" t="n">
         <v>57</v>
       </c>
       <c r="P12" s="27" t="n">
-        <v>41231</v>
+        <v>41745</v>
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
@@ -1501,37 +1564,37 @@
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>35186</v>
+        <v>35262</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>60.9</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>21417</v>
+        <v>21464</v>
       </c>
       <c r="I13" s="24" t="n">
         <v>26.1</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>9179</v>
+        <v>9199</v>
       </c>
       <c r="K13" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="M13" s="26" t="n">
         <v>10.9</v>
       </c>
       <c r="N13" s="26" t="n">
-        <v>3825</v>
+        <v>3833</v>
       </c>
       <c r="O13" s="27" t="n">
         <v>39.1</v>
       </c>
       <c r="P13" s="27" t="n">
-        <v>13768</v>
+        <v>13798</v>
       </c>
       <c r="Q13" s="28" t="inlineStr">
         <is>
@@ -1697,37 +1760,37 @@
         </is>
       </c>
       <c r="F17" s="22" t="n">
-        <v>31665</v>
+        <v>33301</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>47.1</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>14901</v>
+        <v>15671</v>
       </c>
       <c r="I17" s="24" t="n">
         <v>36.5</v>
       </c>
       <c r="J17" s="24" t="n">
-        <v>11548</v>
+        <v>12145</v>
       </c>
       <c r="K17" s="25" t="n">
         <v>10.6</v>
       </c>
       <c r="L17" s="25" t="n">
-        <v>3353</v>
+        <v>3526</v>
       </c>
       <c r="M17" s="26" t="n">
         <v>5.9</v>
       </c>
       <c r="N17" s="26" t="n">
-        <v>1863</v>
+        <v>1959</v>
       </c>
       <c r="O17" s="27" t="n">
         <v>52.9</v>
       </c>
       <c r="P17" s="27" t="n">
-        <v>16764</v>
+        <v>17630</v>
       </c>
       <c r="Q17" s="28" t="inlineStr">
         <is>
@@ -1844,37 +1907,37 @@
         </is>
       </c>
       <c r="F20" s="22" t="n">
-        <v>17648</v>
+        <v>17849</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>46</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>8124</v>
+        <v>8216</v>
       </c>
       <c r="I20" s="24" t="n">
         <v>35.8</v>
       </c>
       <c r="J20" s="24" t="n">
-        <v>6315</v>
+        <v>6387</v>
       </c>
       <c r="K20" s="25" t="n">
         <v>5.4</v>
       </c>
       <c r="L20" s="25" t="n">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="M20" s="26" t="n">
         <v>12.8</v>
       </c>
       <c r="N20" s="26" t="n">
-        <v>2263</v>
+        <v>2288</v>
       </c>
       <c r="O20" s="27" t="n">
         <v>54</v>
       </c>
       <c r="P20" s="27" t="n">
-        <v>9524</v>
+        <v>9632</v>
       </c>
       <c r="Q20" s="28" t="inlineStr">
         <is>
@@ -1942,37 +2005,37 @@
         </is>
       </c>
       <c r="F22" s="22" t="n">
-        <v>37610</v>
+        <v>38707</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>46</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>17313</v>
+        <v>17818</v>
       </c>
       <c r="I22" s="24" t="n">
         <v>35.8</v>
       </c>
       <c r="J22" s="24" t="n">
-        <v>13459</v>
+        <v>13851</v>
       </c>
       <c r="K22" s="25" t="n">
         <v>5.4</v>
       </c>
       <c r="L22" s="25" t="n">
-        <v>2016</v>
+        <v>2075</v>
       </c>
       <c r="M22" s="26" t="n">
         <v>12.8</v>
       </c>
       <c r="N22" s="26" t="n">
-        <v>4822</v>
+        <v>4963</v>
       </c>
       <c r="O22" s="27" t="n">
         <v>54</v>
       </c>
       <c r="P22" s="27" t="n">
-        <v>20297</v>
+        <v>20889</v>
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
@@ -1991,37 +2054,37 @@
         </is>
       </c>
       <c r="F23" s="22" t="n">
-        <v>9012</v>
+        <v>17063</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>46</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>4149</v>
+        <v>7855</v>
       </c>
       <c r="I23" s="24" t="n">
         <v>35.8</v>
       </c>
       <c r="J23" s="24" t="n">
-        <v>3225</v>
+        <v>6106</v>
       </c>
       <c r="K23" s="25" t="n">
         <v>5.4</v>
       </c>
       <c r="L23" s="25" t="n">
-        <v>483</v>
+        <v>915</v>
       </c>
       <c r="M23" s="26" t="n">
         <v>12.8</v>
       </c>
       <c r="N23" s="26" t="n">
-        <v>1155</v>
+        <v>2188</v>
       </c>
       <c r="O23" s="27" t="n">
         <v>54</v>
       </c>
       <c r="P23" s="27" t="n">
-        <v>4864</v>
+        <v>9208</v>
       </c>
       <c r="Q23" s="28" t="inlineStr">
         <is>
@@ -3020,19 +3083,19 @@
         </is>
       </c>
       <c r="F44" s="22" t="n">
-        <v>14915</v>
+        <v>14918</v>
       </c>
       <c r="G44" s="23" t="n">
         <v>75.5</v>
       </c>
       <c r="H44" s="23" t="n">
-        <v>11267</v>
+        <v>11270</v>
       </c>
       <c r="I44" s="24" t="n">
         <v>23.9</v>
       </c>
       <c r="J44" s="24" t="n">
-        <v>3562</v>
+        <v>3563</v>
       </c>
       <c r="K44" s="25" t="n">
         <v>0.3</v>
@@ -3050,7 +3113,7 @@
         <v>24.5</v>
       </c>
       <c r="P44" s="27" t="n">
-        <v>3648</v>
+        <v>3649</v>
       </c>
       <c r="Q44" s="28" t="inlineStr">
         <is>
@@ -3510,19 +3573,19 @@
         </is>
       </c>
       <c r="F54" s="22" t="n">
-        <v>17900</v>
+        <v>18013</v>
       </c>
       <c r="G54" s="23" t="n">
         <v>75.5</v>
       </c>
       <c r="H54" s="23" t="n">
-        <v>13522</v>
+        <v>13607</v>
       </c>
       <c r="I54" s="24" t="n">
         <v>23.9</v>
       </c>
       <c r="J54" s="24" t="n">
-        <v>4275</v>
+        <v>4302</v>
       </c>
       <c r="K54" s="25" t="n">
         <v>0.3</v>
@@ -3540,7 +3603,7 @@
         <v>24.5</v>
       </c>
       <c r="P54" s="27" t="n">
-        <v>4378</v>
+        <v>4406</v>
       </c>
       <c r="Q54" s="28" t="inlineStr">
         <is>
@@ -4294,37 +4357,37 @@
         </is>
       </c>
       <c r="F70" s="22" t="n">
-        <v>11504</v>
+        <v>11768</v>
       </c>
       <c r="G70" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H70" s="23" t="n">
-        <v>3863</v>
+        <v>3952</v>
       </c>
       <c r="I70" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J70" s="24" t="n">
-        <v>7184</v>
+        <v>7348</v>
       </c>
       <c r="K70" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L70" s="25" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M70" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N70" s="26" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="O70" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P70" s="27" t="n">
-        <v>7641</v>
+        <v>7816</v>
       </c>
       <c r="Q70" s="28" t="inlineStr">
         <is>
@@ -4343,37 +4406,37 @@
         </is>
       </c>
       <c r="F71" s="22" t="n">
-        <v>46342</v>
+        <v>46397</v>
       </c>
       <c r="G71" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H71" s="23" t="n">
-        <v>15562</v>
+        <v>15580</v>
       </c>
       <c r="I71" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J71" s="24" t="n">
-        <v>28938</v>
+        <v>28972</v>
       </c>
       <c r="K71" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L71" s="25" t="n">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="M71" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N71" s="26" t="n">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="O71" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P71" s="27" t="n">
-        <v>30781</v>
+        <v>30817</v>
       </c>
       <c r="Q71" s="28" t="inlineStr">
         <is>
@@ -4392,37 +4455,37 @@
         </is>
       </c>
       <c r="F72" s="22" t="n">
-        <v>9518</v>
+        <v>9671</v>
       </c>
       <c r="G72" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H72" s="23" t="n">
-        <v>3196</v>
+        <v>3248</v>
       </c>
       <c r="I72" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J72" s="24" t="n">
-        <v>5943</v>
+        <v>6039</v>
       </c>
       <c r="K72" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L72" s="25" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="M72" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N72" s="26" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="O72" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P72" s="27" t="n">
-        <v>6322</v>
+        <v>6424</v>
       </c>
       <c r="Q72" s="28" t="inlineStr">
         <is>
@@ -4490,37 +4553,37 @@
         </is>
       </c>
       <c r="F74" s="22" t="n">
-        <v>74581</v>
+        <v>75532</v>
       </c>
       <c r="G74" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H74" s="23" t="n">
-        <v>25044</v>
+        <v>25363</v>
       </c>
       <c r="I74" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J74" s="24" t="n">
-        <v>46572</v>
+        <v>47166</v>
       </c>
       <c r="K74" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L74" s="25" t="n">
-        <v>1619</v>
+        <v>1640</v>
       </c>
       <c r="M74" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N74" s="26" t="n">
-        <v>1346</v>
+        <v>1363</v>
       </c>
       <c r="O74" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P74" s="27" t="n">
-        <v>49537</v>
+        <v>50169</v>
       </c>
       <c r="Q74" s="28" t="inlineStr">
         <is>
@@ -4539,37 +4602,37 @@
         </is>
       </c>
       <c r="F75" s="22" t="n">
-        <v>38224</v>
+        <v>39846</v>
       </c>
       <c r="G75" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H75" s="23" t="n">
-        <v>12836</v>
+        <v>13380</v>
       </c>
       <c r="I75" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J75" s="24" t="n">
-        <v>23869</v>
+        <v>24882</v>
       </c>
       <c r="K75" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L75" s="25" t="n">
-        <v>830</v>
+        <v>865</v>
       </c>
       <c r="M75" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N75" s="26" t="n">
-        <v>690</v>
+        <v>719</v>
       </c>
       <c r="O75" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P75" s="27" t="n">
-        <v>25389</v>
+        <v>26466</v>
       </c>
       <c r="Q75" s="28" t="inlineStr">
         <is>
@@ -4637,37 +4700,37 @@
         </is>
       </c>
       <c r="F77" s="22" t="n">
-        <v>46871</v>
+        <v>49530</v>
       </c>
       <c r="G77" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H77" s="23" t="n">
-        <v>15739</v>
+        <v>16632</v>
       </c>
       <c r="I77" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J77" s="24" t="n">
-        <v>29268</v>
+        <v>30929</v>
       </c>
       <c r="K77" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L77" s="25" t="n">
-        <v>1018</v>
+        <v>1075</v>
       </c>
       <c r="M77" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N77" s="26" t="n">
-        <v>846</v>
+        <v>894</v>
       </c>
       <c r="O77" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P77" s="27" t="n">
-        <v>31132</v>
+        <v>32898</v>
       </c>
       <c r="Q77" s="28" t="inlineStr">
         <is>
@@ -4686,37 +4749,37 @@
         </is>
       </c>
       <c r="F78" s="22" t="n">
-        <v>42929</v>
+        <v>43008</v>
       </c>
       <c r="G78" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H78" s="23" t="n">
-        <v>14415</v>
+        <v>14442</v>
       </c>
       <c r="I78" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J78" s="24" t="n">
-        <v>26807</v>
+        <v>26856</v>
       </c>
       <c r="K78" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L78" s="25" t="n">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="M78" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N78" s="26" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O78" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P78" s="27" t="n">
-        <v>28514</v>
+        <v>28566</v>
       </c>
       <c r="Q78" s="28" t="inlineStr">
         <is>
@@ -4735,37 +4798,37 @@
         </is>
       </c>
       <c r="F79" s="22" t="n">
-        <v>4999</v>
+        <v>5093</v>
       </c>
       <c r="G79" s="23" t="n">
         <v>33.6</v>
       </c>
       <c r="H79" s="23" t="n">
-        <v>1679</v>
+        <v>1710</v>
       </c>
       <c r="I79" s="24" t="n">
         <v>62.4</v>
       </c>
       <c r="J79" s="24" t="n">
-        <v>3122</v>
+        <v>3181</v>
       </c>
       <c r="K79" s="25" t="n">
         <v>2.2</v>
       </c>
       <c r="L79" s="25" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M79" s="26" t="n">
         <v>1.8</v>
       </c>
       <c r="N79" s="26" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O79" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
       <c r="P79" s="27" t="n">
-        <v>3321</v>
+        <v>3383</v>
       </c>
       <c r="Q79" s="28" t="inlineStr">
         <is>
@@ -4931,37 +4994,37 @@
         </is>
       </c>
       <c r="F83" s="22" t="n">
-        <v>46047</v>
+        <v>46063</v>
       </c>
       <c r="G83" s="23" t="n">
         <v>34.6</v>
       </c>
       <c r="H83" s="23" t="n">
-        <v>15924</v>
+        <v>15930</v>
       </c>
       <c r="I83" s="24" t="n">
         <v>53</v>
       </c>
       <c r="J83" s="24" t="n">
-        <v>24427</v>
+        <v>24435</v>
       </c>
       <c r="K83" s="25" t="n">
         <v>5.8</v>
       </c>
       <c r="L83" s="25" t="n">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="M83" s="26" t="n">
         <v>6.6</v>
       </c>
       <c r="N83" s="26" t="n">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="O83" s="27" t="n">
         <v>65.40000000000001</v>
       </c>
       <c r="P83" s="27" t="n">
-        <v>30123</v>
+        <v>30134</v>
       </c>
       <c r="Q83" s="28" t="inlineStr">
         <is>
@@ -5176,37 +5239,37 @@
         </is>
       </c>
       <c r="F88" s="22" t="n">
-        <v>15005</v>
+        <v>15035</v>
       </c>
       <c r="G88" s="23" t="n">
         <v>34.6</v>
       </c>
       <c r="H88" s="23" t="n">
-        <v>5189</v>
+        <v>5199</v>
       </c>
       <c r="I88" s="24" t="n">
         <v>53</v>
       </c>
       <c r="J88" s="24" t="n">
-        <v>7960</v>
+        <v>7976</v>
       </c>
       <c r="K88" s="25" t="n">
         <v>5.8</v>
       </c>
       <c r="L88" s="25" t="n">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="M88" s="26" t="n">
         <v>6.6</v>
       </c>
       <c r="N88" s="26" t="n">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="O88" s="27" t="n">
         <v>65.40000000000001</v>
       </c>
       <c r="P88" s="27" t="n">
-        <v>9816</v>
+        <v>9836</v>
       </c>
       <c r="Q88" s="28" t="inlineStr">
         <is>
@@ -5225,19 +5288,19 @@
         </is>
       </c>
       <c r="F89" s="22" t="n">
-        <v>24042</v>
+        <v>24043</v>
       </c>
       <c r="G89" s="23" t="n">
         <v>34.6</v>
       </c>
       <c r="H89" s="23" t="n">
-        <v>8314</v>
+        <v>8315</v>
       </c>
       <c r="I89" s="24" t="n">
         <v>53</v>
       </c>
       <c r="J89" s="24" t="n">
-        <v>12753</v>
+        <v>12754</v>
       </c>
       <c r="K89" s="25" t="n">
         <v>5.8</v>
@@ -5274,37 +5337,37 @@
         </is>
       </c>
       <c r="F90" s="22" t="n">
-        <v>17431</v>
+        <v>19591</v>
       </c>
       <c r="G90" s="23" t="n">
         <v>34.6</v>
       </c>
       <c r="H90" s="23" t="n">
-        <v>6028</v>
+        <v>6775</v>
       </c>
       <c r="I90" s="24" t="n">
         <v>53</v>
       </c>
       <c r="J90" s="24" t="n">
-        <v>9247</v>
+        <v>10392</v>
       </c>
       <c r="K90" s="25" t="n">
         <v>5.8</v>
       </c>
       <c r="L90" s="25" t="n">
-        <v>1009</v>
+        <v>1134</v>
       </c>
       <c r="M90" s="26" t="n">
         <v>6.6</v>
       </c>
       <c r="N90" s="26" t="n">
-        <v>1148</v>
+        <v>1290</v>
       </c>
       <c r="O90" s="27" t="n">
         <v>65.40000000000001</v>
       </c>
       <c r="P90" s="27" t="n">
-        <v>11403</v>
+        <v>12816</v>
       </c>
       <c r="Q90" s="28" t="inlineStr">
         <is>
@@ -6303,25 +6366,25 @@
         </is>
       </c>
       <c r="F111" s="22" t="n">
-        <v>11557</v>
+        <v>12085</v>
       </c>
       <c r="G111" s="23" t="n">
         <v>56.4</v>
       </c>
       <c r="H111" s="23" t="n">
-        <v>6515</v>
+        <v>6813</v>
       </c>
       <c r="I111" s="24" t="n">
         <v>41.1</v>
       </c>
       <c r="J111" s="24" t="n">
-        <v>4750</v>
+        <v>4967</v>
       </c>
       <c r="K111" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="L111" s="25" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="M111" s="26" t="n">
         <v>0</v>
@@ -6333,7 +6396,7 @@
         <v>43.6</v>
       </c>
       <c r="P111" s="27" t="n">
-        <v>5042</v>
+        <v>5272</v>
       </c>
       <c r="Q111" s="28" t="inlineStr">
         <is>
@@ -6352,25 +6415,25 @@
         </is>
       </c>
       <c r="F112" s="22" t="n">
-        <v>5453</v>
+        <v>8385</v>
       </c>
       <c r="G112" s="23" t="n">
         <v>56.4</v>
       </c>
       <c r="H112" s="23" t="n">
-        <v>3074</v>
+        <v>4727</v>
       </c>
       <c r="I112" s="24" t="n">
         <v>41.1</v>
       </c>
       <c r="J112" s="24" t="n">
-        <v>2241</v>
+        <v>3446</v>
       </c>
       <c r="K112" s="25" t="n">
         <v>2.5</v>
       </c>
       <c r="L112" s="25" t="n">
-        <v>138</v>
+        <v>212</v>
       </c>
       <c r="M112" s="26" t="n">
         <v>0</v>
@@ -6382,7 +6445,7 @@
         <v>43.6</v>
       </c>
       <c r="P112" s="27" t="n">
-        <v>2379</v>
+        <v>3658</v>
       </c>
       <c r="Q112" s="28" t="inlineStr">
         <is>
@@ -23379,6 +23442,7685 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R145"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="37" customWidth="1" min="14" max="14"/>
+    <col width="37" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>PiN -- Retourné (5-17 ans)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="14" t="n"/>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>admin2</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>% niveaux de sévérité 1-2</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t># niveaux de sévérité 1-2</t>
+        </is>
+      </c>
+      <c r="H5" s="17" t="inlineStr">
+        <is>
+          <t>% niveau de sévérité 3</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t># niveau de sévérité 3</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
+        <is>
+          <t>% niveau de sévérité 4</t>
+        </is>
+      </c>
+      <c r="K5" s="18" t="inlineStr">
+        <is>
+          <t># niveau de sévérité 4</t>
+        </is>
+      </c>
+      <c r="L5" s="19" t="inlineStr">
+        <is>
+          <t>% niveau de sévérité 5</t>
+        </is>
+      </c>
+      <c r="M5" s="19" t="inlineStr">
+        <is>
+          <t># niveau de sévérité 5</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>% Tot PiN (niveaux de sévérité 3-5)</t>
+        </is>
+      </c>
+      <c r="O5" s="20" t="inlineStr">
+        <is>
+          <t># Tot PiN (niveaux de sévérité 3-5)</t>
+        </is>
+      </c>
+      <c r="P5" s="20" t="inlineStr">
+        <is>
+          <t>Sévérité de la zone</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
+        <is>
+          <t>Groupe de population</t>
+        </is>
+      </c>
+      <c r="R5" s="15" t="inlineStr">
+        <is>
+          <t>Population totale</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="n"/>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>HT0111</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>478</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>222</v>
+      </c>
+      <c r="J6" s="25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="25" t="n">
+        <v>102</v>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="M6" s="26" t="n">
+        <v>410</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="O6" s="27" t="n">
+        <v>734</v>
+      </c>
+      <c r="P6" s="27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R6" s="35" t="n">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>HT0112</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>79</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I7" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="M7" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="N7" s="27" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="O7" s="27" t="n">
+        <v>51</v>
+      </c>
+      <c r="P7" s="27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q7" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R7" s="35" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>HT0113</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="27" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="O8" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q8" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R8" s="35" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>HT0114</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="J9" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M9" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="27" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="O9" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="P9" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R9" s="35" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>HT0117</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>43</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>388</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>388</v>
+      </c>
+      <c r="J10" s="25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K10" s="25" t="n">
+        <v>47</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="M10" s="26" t="n">
+        <v>79</v>
+      </c>
+      <c r="N10" s="27" t="n">
+        <v>57</v>
+      </c>
+      <c r="O10" s="27" t="n">
+        <v>514</v>
+      </c>
+      <c r="P10" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q10" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R10" s="35" t="n">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n"/>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>HT0118</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K11" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M11" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" s="27" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="O11" s="27" t="n">
+        <v>30</v>
+      </c>
+      <c r="P11" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q11" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R11" s="35" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n"/>
+      <c r="B12" s="21" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>HT0131</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>770</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>597</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K12" s="25" t="n">
+        <v>173</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M12" s="26" t="n">
+        <v>96</v>
+      </c>
+      <c r="N12" s="27" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="O12" s="27" t="n">
+        <v>866</v>
+      </c>
+      <c r="P12" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R12" s="35" t="n">
+        <v>1637</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>HT0115</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>82</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>63</v>
+      </c>
+      <c r="J13" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K13" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M13" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="N13" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O13" s="27" t="n">
+        <v>96</v>
+      </c>
+      <c r="P13" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q13" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R13" s="35" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>HT0116</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q14" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R14" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="n"/>
+      <c r="B15" s="21" t="n"/>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>HT0121</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O15" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q15" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R15" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n"/>
+      <c r="B16" s="21" t="n"/>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>HT0122</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q16" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R16" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="n"/>
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>HT0123</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O17" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q17" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R17" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n"/>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>HT0132</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q18" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R18" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n"/>
+      <c r="B19" s="21" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>HT0133</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I19" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q19" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R19" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>HT0134</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>93</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I20" s="24" t="n">
+        <v>72</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M20" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="N20" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O20" s="27" t="n">
+        <v>109</v>
+      </c>
+      <c r="P20" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q20" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R20" s="35" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>HT0135</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G21" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I21" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q21" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R21" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>HT0141</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G22" s="23" t="n">
+        <v>505</v>
+      </c>
+      <c r="H22" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I22" s="24" t="n">
+        <v>392</v>
+      </c>
+      <c r="J22" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K22" s="25" t="n">
+        <v>59</v>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M22" s="26" t="n">
+        <v>141</v>
+      </c>
+      <c r="N22" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O22" s="27" t="n">
+        <v>592</v>
+      </c>
+      <c r="P22" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R22" s="35" t="n">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="n"/>
+      <c r="B23" s="21" t="n"/>
+      <c r="C23" s="21" t="n"/>
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>HT0142</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G23" s="23" t="n">
+        <v>3706</v>
+      </c>
+      <c r="H23" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I23" s="24" t="n">
+        <v>2881</v>
+      </c>
+      <c r="J23" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K23" s="25" t="n">
+        <v>432</v>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M23" s="26" t="n">
+        <v>1032</v>
+      </c>
+      <c r="N23" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O23" s="27" t="n">
+        <v>4345</v>
+      </c>
+      <c r="P23" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q23" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R23" s="35" t="n">
+        <v>8051</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="n"/>
+      <c r="B24" s="21" t="n"/>
+      <c r="C24" s="21" t="n"/>
+      <c r="D24" s="21" t="n"/>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>HT0151</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q24" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R24" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="n"/>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>HT0152</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="n">
+        <v>46</v>
+      </c>
+      <c r="G25" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="24" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I25" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K25" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="M25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="27" t="n">
+        <v>54</v>
+      </c>
+      <c r="O25" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q25" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R25" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="n"/>
+      <c r="B26" s="21" t="n"/>
+      <c r="C26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>HT0211</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G26" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K26" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O26" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q26" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R26" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="n"/>
+      <c r="B27" s="21" t="n"/>
+      <c r="C27" s="21" t="n"/>
+      <c r="D27" s="21" t="n"/>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>HT0212</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G27" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K27" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q27" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R27" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="n"/>
+      <c r="B28" s="21" t="n"/>
+      <c r="C28" s="21" t="n"/>
+      <c r="D28" s="21" t="n"/>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>HT0213</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G28" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q28" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R28" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="n"/>
+      <c r="B29" s="21" t="n"/>
+      <c r="C29" s="21" t="n"/>
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>HT0214</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K29" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q29" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R29" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="n"/>
+      <c r="B30" s="21" t="n"/>
+      <c r="C30" s="21" t="n"/>
+      <c r="D30" s="21" t="n"/>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>HT0221</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q30" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R30" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="n"/>
+      <c r="B31" s="21" t="n"/>
+      <c r="C31" s="21" t="n"/>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>HT0222</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q31" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R31" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="n"/>
+      <c r="B32" s="21" t="n"/>
+      <c r="C32" s="21" t="n"/>
+      <c r="D32" s="21" t="n"/>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>HT0231</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K32" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q32" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R32" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="n"/>
+      <c r="B33" s="21" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="21" t="n"/>
+      <c r="E33" s="22" t="inlineStr">
+        <is>
+          <t>HT0232</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q33" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R33" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="n"/>
+      <c r="B34" s="21" t="n"/>
+      <c r="C34" s="21" t="n"/>
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="22" t="inlineStr">
+        <is>
+          <t>HT0233</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G34" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q34" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R34" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="n"/>
+      <c r="B35" s="21" t="n"/>
+      <c r="C35" s="21" t="n"/>
+      <c r="D35" s="21" t="n"/>
+      <c r="E35" s="22" t="inlineStr">
+        <is>
+          <t>HT0234</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="G35" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="24" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="27" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="O35" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q35" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R35" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="n"/>
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="22" t="inlineStr">
+        <is>
+          <t>HT0311</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G36" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K36" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O36" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q36" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R36" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="n"/>
+      <c r="B37" s="21" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="21" t="n"/>
+      <c r="E37" s="22" t="inlineStr">
+        <is>
+          <t>HT0312</t>
+        </is>
+      </c>
+      <c r="F37" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G37" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O37" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q37" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R37" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="n"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="21" t="n"/>
+      <c r="D38" s="21" t="n"/>
+      <c r="E38" s="22" t="inlineStr">
+        <is>
+          <t>HT0313</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O38" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q38" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R38" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="n"/>
+      <c r="B39" s="21" t="n"/>
+      <c r="C39" s="21" t="n"/>
+      <c r="D39" s="21" t="n"/>
+      <c r="E39" s="22" t="inlineStr">
+        <is>
+          <t>HT0321</t>
+        </is>
+      </c>
+      <c r="F39" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G39" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O39" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q39" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R39" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="n"/>
+      <c r="B40" s="21" t="n"/>
+      <c r="C40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="22" t="inlineStr">
+        <is>
+          <t>HT0322</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O40" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q40" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R40" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="n"/>
+      <c r="B41" s="21" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="21" t="n"/>
+      <c r="E41" s="22" t="inlineStr">
+        <is>
+          <t>HT0323</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O41" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q41" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R41" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="n"/>
+      <c r="B42" s="21" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="22" t="inlineStr">
+        <is>
+          <t>HT0331</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O42" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q42" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R42" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="n"/>
+      <c r="B43" s="21" t="n"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="22" t="inlineStr">
+        <is>
+          <t>HT0332</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O43" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q43" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R43" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="n"/>
+      <c r="B44" s="21" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>HT0341</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O44" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q44" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R44" s="35" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="n"/>
+      <c r="B45" s="21" t="n"/>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>HT0342</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O45" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q45" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R45" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="n"/>
+      <c r="B46" s="21" t="n"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>HT0343</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O46" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q46" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R46" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="21" t="n"/>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="22" t="inlineStr">
+        <is>
+          <t>HT0344</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I47" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O47" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q47" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R47" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="n"/>
+      <c r="B48" s="21" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>HT0345</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I48" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O48" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q48" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R48" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="n"/>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="22" t="inlineStr">
+        <is>
+          <t>HT0351</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I49" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O49" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q49" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R49" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="n"/>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>HT0352</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G50" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I50" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O50" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q50" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R50" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="n"/>
+      <c r="B51" s="21" t="n"/>
+      <c r="C51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="22" t="inlineStr">
+        <is>
+          <t>HT0361</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G51" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I51" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O51" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q51" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R51" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="n"/>
+      <c r="B52" s="21" t="n"/>
+      <c r="C52" s="21" t="n"/>
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>HT0362</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I52" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O52" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q52" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R52" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="n"/>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="22" t="inlineStr">
+        <is>
+          <t>HT0371</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G53" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I53" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O53" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q53" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R53" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="n"/>
+      <c r="B54" s="21" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="21" t="n"/>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>HT0372</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="G54" s="23" t="n">
+        <v>86</v>
+      </c>
+      <c r="H54" s="24" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I54" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="J54" s="25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="27" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="O54" s="27" t="n">
+        <v>28</v>
+      </c>
+      <c r="P54" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q54" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R54" s="35" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="n"/>
+      <c r="B55" s="21" t="n"/>
+      <c r="C55" s="21" t="n"/>
+      <c r="D55" s="21" t="n"/>
+      <c r="E55" s="22" t="inlineStr">
+        <is>
+          <t>HT0411</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G55" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I55" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O55" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q55" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R55" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="n"/>
+      <c r="B56" s="21" t="n"/>
+      <c r="C56" s="21" t="n"/>
+      <c r="D56" s="21" t="n"/>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>HT0412</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I56" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O56" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q56" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R56" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="21" t="n"/>
+      <c r="B57" s="21" t="n"/>
+      <c r="C57" s="21" t="n"/>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="22" t="inlineStr">
+        <is>
+          <t>HT0413</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I57" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O57" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q57" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R57" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="21" t="n"/>
+      <c r="B58" s="21" t="n"/>
+      <c r="C58" s="21" t="n"/>
+      <c r="D58" s="21" t="n"/>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>HT0421</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G58" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I58" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O58" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q58" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R58" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="21" t="n"/>
+      <c r="B59" s="21" t="n"/>
+      <c r="C59" s="21" t="n"/>
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="22" t="inlineStr">
+        <is>
+          <t>HT0422</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G59" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I59" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O59" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q59" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R59" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="21" t="n"/>
+      <c r="B60" s="21" t="n"/>
+      <c r="C60" s="21" t="n"/>
+      <c r="D60" s="21" t="n"/>
+      <c r="E60" s="22" t="inlineStr">
+        <is>
+          <t>HT0423</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G60" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I60" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O60" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q60" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R60" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="21" t="n"/>
+      <c r="B61" s="21" t="n"/>
+      <c r="C61" s="21" t="n"/>
+      <c r="D61" s="21" t="n"/>
+      <c r="E61" s="22" t="inlineStr">
+        <is>
+          <t>HT0431</t>
+        </is>
+      </c>
+      <c r="F61" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G61" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I61" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O61" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q61" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R61" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="n"/>
+      <c r="B62" s="21" t="n"/>
+      <c r="C62" s="21" t="n"/>
+      <c r="D62" s="21" t="n"/>
+      <c r="E62" s="22" t="inlineStr">
+        <is>
+          <t>HT0432</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I62" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O62" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q62" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R62" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="n"/>
+      <c r="B63" s="21" t="n"/>
+      <c r="C63" s="21" t="n"/>
+      <c r="D63" s="21" t="n"/>
+      <c r="E63" s="22" t="inlineStr">
+        <is>
+          <t>HT0433</t>
+        </is>
+      </c>
+      <c r="F63" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G63" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I63" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O63" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q63" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R63" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="n"/>
+      <c r="B64" s="21" t="n"/>
+      <c r="C64" s="21" t="n"/>
+      <c r="D64" s="21" t="n"/>
+      <c r="E64" s="22" t="inlineStr">
+        <is>
+          <t>HT0434</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G64" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I64" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O64" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q64" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R64" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="n"/>
+      <c r="B65" s="21" t="n"/>
+      <c r="C65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="22" t="inlineStr">
+        <is>
+          <t>HT0441</t>
+        </is>
+      </c>
+      <c r="F65" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G65" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I65" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O65" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q65" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R65" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="n"/>
+      <c r="B66" s="21" t="n"/>
+      <c r="C66" s="21" t="n"/>
+      <c r="D66" s="21" t="n"/>
+      <c r="E66" s="22" t="inlineStr">
+        <is>
+          <t>HT0442</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G66" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I66" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O66" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q66" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R66" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="21" t="n"/>
+      <c r="B67" s="21" t="n"/>
+      <c r="C67" s="21" t="n"/>
+      <c r="D67" s="21" t="n"/>
+      <c r="E67" s="22" t="inlineStr">
+        <is>
+          <t>HT0443</t>
+        </is>
+      </c>
+      <c r="F67" s="23" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G67" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="24" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="I67" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="O67" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q67" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R67" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="n"/>
+      <c r="B68" s="21" t="n"/>
+      <c r="C68" s="21" t="n"/>
+      <c r="D68" s="21" t="n"/>
+      <c r="E68" s="22" t="inlineStr">
+        <is>
+          <t>HT0511</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G68" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I68" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K68" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O68" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q68" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R68" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="21" t="n"/>
+      <c r="B69" s="21" t="n"/>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="21" t="n"/>
+      <c r="E69" s="22" t="inlineStr">
+        <is>
+          <t>HT0512</t>
+        </is>
+      </c>
+      <c r="F69" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G69" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I69" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K69" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O69" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q69" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R69" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="21" t="n"/>
+      <c r="B70" s="21" t="n"/>
+      <c r="C70" s="21" t="n"/>
+      <c r="D70" s="21" t="n"/>
+      <c r="E70" s="22" t="inlineStr">
+        <is>
+          <t>HT0513</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G70" s="23" t="n">
+        <v>88</v>
+      </c>
+      <c r="H70" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I70" s="24" t="n">
+        <v>164</v>
+      </c>
+      <c r="J70" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K70" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M70" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="N70" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O70" s="27" t="n">
+        <v>175</v>
+      </c>
+      <c r="P70" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q70" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R70" s="35" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="21" t="n"/>
+      <c r="B71" s="21" t="n"/>
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="21" t="n"/>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>HT0521</t>
+        </is>
+      </c>
+      <c r="F71" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G71" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="H71" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I71" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="J71" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K71" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M71" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O71" s="27" t="n">
+        <v>36</v>
+      </c>
+      <c r="P71" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q71" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R71" s="35" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="21" t="n"/>
+      <c r="B72" s="21" t="n"/>
+      <c r="C72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>HT0522</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G72" s="23" t="n">
+        <v>51</v>
+      </c>
+      <c r="H72" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I72" s="24" t="n">
+        <v>96</v>
+      </c>
+      <c r="J72" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K72" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M72" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O72" s="27" t="n">
+        <v>102</v>
+      </c>
+      <c r="P72" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q72" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R72" s="35" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="21" t="n"/>
+      <c r="B73" s="21" t="n"/>
+      <c r="C73" s="21" t="n"/>
+      <c r="D73" s="21" t="n"/>
+      <c r="E73" s="22" t="inlineStr">
+        <is>
+          <t>HT0523</t>
+        </is>
+      </c>
+      <c r="F73" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G73" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I73" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K73" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M73" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O73" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q73" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R73" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="n"/>
+      <c r="B74" s="21" t="n"/>
+      <c r="C74" s="21" t="n"/>
+      <c r="D74" s="21" t="n"/>
+      <c r="E74" s="22" t="inlineStr">
+        <is>
+          <t>HT0531</t>
+        </is>
+      </c>
+      <c r="F74" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G74" s="23" t="n">
+        <v>319</v>
+      </c>
+      <c r="H74" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I74" s="24" t="n">
+        <v>594</v>
+      </c>
+      <c r="J74" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K74" s="25" t="n">
+        <v>21</v>
+      </c>
+      <c r="L74" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M74" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="N74" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O74" s="27" t="n">
+        <v>632</v>
+      </c>
+      <c r="P74" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q74" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R74" s="35" t="n">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="n"/>
+      <c r="B75" s="21" t="n"/>
+      <c r="C75" s="21" t="n"/>
+      <c r="D75" s="21" t="n"/>
+      <c r="E75" s="22" t="inlineStr">
+        <is>
+          <t>HT0532</t>
+        </is>
+      </c>
+      <c r="F75" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G75" s="23" t="n">
+        <v>545</v>
+      </c>
+      <c r="H75" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I75" s="24" t="n">
+        <v>1013</v>
+      </c>
+      <c r="J75" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K75" s="25" t="n">
+        <v>35</v>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M75" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="N75" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O75" s="27" t="n">
+        <v>1077</v>
+      </c>
+      <c r="P75" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q75" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R75" s="35" t="n">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="n"/>
+      <c r="B76" s="21" t="n"/>
+      <c r="C76" s="21" t="n"/>
+      <c r="D76" s="21" t="n"/>
+      <c r="E76" s="22" t="inlineStr">
+        <is>
+          <t>HT0533</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G76" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I76" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M76" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O76" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q76" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R76" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="n"/>
+      <c r="B77" s="21" t="n"/>
+      <c r="C77" s="21" t="n"/>
+      <c r="D77" s="21" t="n"/>
+      <c r="E77" s="22" t="inlineStr">
+        <is>
+          <t>HT0541</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>893</v>
+      </c>
+      <c r="H77" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I77" s="24" t="n">
+        <v>1661</v>
+      </c>
+      <c r="J77" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K77" s="25" t="n">
+        <v>58</v>
+      </c>
+      <c r="L77" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M77" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="N77" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O77" s="27" t="n">
+        <v>1766</v>
+      </c>
+      <c r="P77" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q77" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R77" s="35" t="n">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="n"/>
+      <c r="B78" s="21" t="n"/>
+      <c r="C78" s="21" t="n"/>
+      <c r="D78" s="21" t="n"/>
+      <c r="E78" s="22" t="inlineStr">
+        <is>
+          <t>HT0542</t>
+        </is>
+      </c>
+      <c r="F78" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G78" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="H78" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I78" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="J78" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K78" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M78" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O78" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="P78" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q78" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R78" s="35" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="n"/>
+      <c r="B79" s="21" t="n"/>
+      <c r="C79" s="21" t="n"/>
+      <c r="D79" s="21" t="n"/>
+      <c r="E79" s="22" t="inlineStr">
+        <is>
+          <t>HT0543</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="H79" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I79" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="J79" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K79" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M79" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N79" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O79" s="27" t="n">
+        <v>62</v>
+      </c>
+      <c r="P79" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q79" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R79" s="35" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="n"/>
+      <c r="B80" s="21" t="n"/>
+      <c r="C80" s="21" t="n"/>
+      <c r="D80" s="21" t="n"/>
+      <c r="E80" s="22" t="inlineStr">
+        <is>
+          <t>HT0544</t>
+        </is>
+      </c>
+      <c r="F80" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G80" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I80" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K80" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M80" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O80" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q80" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R80" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="21" t="n"/>
+      <c r="B81" s="21" t="n"/>
+      <c r="C81" s="21" t="n"/>
+      <c r="D81" s="21" t="n"/>
+      <c r="E81" s="22" t="inlineStr">
+        <is>
+          <t>HT0551</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G81" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I81" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K81" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M81" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O81" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q81" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R81" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="21" t="n"/>
+      <c r="B82" s="21" t="n"/>
+      <c r="C82" s="21" t="n"/>
+      <c r="D82" s="21" t="n"/>
+      <c r="E82" s="22" t="inlineStr">
+        <is>
+          <t>HT0552</t>
+        </is>
+      </c>
+      <c r="F82" s="23" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="G82" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="24" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="I82" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K82" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M82" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="27" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="O82" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q82" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R82" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="21" t="n"/>
+      <c r="B83" s="21" t="n"/>
+      <c r="C83" s="21" t="n"/>
+      <c r="D83" s="21" t="n"/>
+      <c r="E83" s="22" t="inlineStr">
+        <is>
+          <t>HT0611</t>
+        </is>
+      </c>
+      <c r="F83" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G83" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="H83" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I83" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J83" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K83" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M83" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O83" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="P83" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q83" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R83" s="35" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="21" t="n"/>
+      <c r="B84" s="21" t="n"/>
+      <c r="C84" s="21" t="n"/>
+      <c r="D84" s="21" t="n"/>
+      <c r="E84" s="22" t="inlineStr">
+        <is>
+          <t>HT0612</t>
+        </is>
+      </c>
+      <c r="F84" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G84" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I84" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K84" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M84" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O84" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q84" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R84" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="21" t="n"/>
+      <c r="B85" s="21" t="n"/>
+      <c r="C85" s="21" t="n"/>
+      <c r="D85" s="21" t="n"/>
+      <c r="E85" s="22" t="inlineStr">
+        <is>
+          <t>HT0613</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G85" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I85" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K85" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M85" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O85" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q85" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R85" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="n"/>
+      <c r="B86" s="21" t="n"/>
+      <c r="C86" s="21" t="n"/>
+      <c r="D86" s="21" t="n"/>
+      <c r="E86" s="22" t="inlineStr">
+        <is>
+          <t>HT0614</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G86" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I86" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K86" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M86" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O86" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q86" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R86" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="n"/>
+      <c r="B87" s="21" t="n"/>
+      <c r="C87" s="21" t="n"/>
+      <c r="D87" s="21" t="n"/>
+      <c r="E87" s="22" t="inlineStr">
+        <is>
+          <t>HT0621</t>
+        </is>
+      </c>
+      <c r="F87" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G87" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I87" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M87" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O87" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q87" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R87" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="n"/>
+      <c r="B88" s="21" t="n"/>
+      <c r="C88" s="21" t="n"/>
+      <c r="D88" s="21" t="n"/>
+      <c r="E88" s="22" t="inlineStr">
+        <is>
+          <t>HT0622</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G88" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H88" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I88" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="J88" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K88" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M88" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N88" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O88" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="P88" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q88" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R88" s="35" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="n"/>
+      <c r="B89" s="21" t="n"/>
+      <c r="C89" s="21" t="n"/>
+      <c r="D89" s="21" t="n"/>
+      <c r="E89" s="22" t="inlineStr">
+        <is>
+          <t>HT0623</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G89" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I89" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K89" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M89" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O89" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q89" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R89" s="35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="n"/>
+      <c r="B90" s="21" t="n"/>
+      <c r="C90" s="21" t="n"/>
+      <c r="D90" s="21" t="n"/>
+      <c r="E90" s="22" t="inlineStr">
+        <is>
+          <t>HT0631</t>
+        </is>
+      </c>
+      <c r="F90" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G90" s="23" t="n">
+        <v>747</v>
+      </c>
+      <c r="H90" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I90" s="24" t="n">
+        <v>1146</v>
+      </c>
+      <c r="J90" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K90" s="25" t="n">
+        <v>125</v>
+      </c>
+      <c r="L90" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M90" s="26" t="n">
+        <v>142</v>
+      </c>
+      <c r="N90" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O90" s="27" t="n">
+        <v>1413</v>
+      </c>
+      <c r="P90" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q90" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R90" s="35" t="n">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="n"/>
+      <c r="B91" s="21" t="n"/>
+      <c r="C91" s="21" t="n"/>
+      <c r="D91" s="21" t="n"/>
+      <c r="E91" s="22" t="inlineStr">
+        <is>
+          <t>HT0632</t>
+        </is>
+      </c>
+      <c r="F91" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G91" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I91" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K91" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M91" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O91" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q91" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R91" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="n"/>
+      <c r="B92" s="21" t="n"/>
+      <c r="C92" s="21" t="n"/>
+      <c r="D92" s="21" t="n"/>
+      <c r="E92" s="22" t="inlineStr">
+        <is>
+          <t>HT0633</t>
+        </is>
+      </c>
+      <c r="F92" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G92" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I92" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K92" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M92" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O92" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q92" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R92" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="21" t="n"/>
+      <c r="B93" s="21" t="n"/>
+      <c r="C93" s="21" t="n"/>
+      <c r="D93" s="21" t="n"/>
+      <c r="E93" s="22" t="inlineStr">
+        <is>
+          <t>HT0641</t>
+        </is>
+      </c>
+      <c r="F93" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G93" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I93" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K93" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M93" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O93" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q93" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R93" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="21" t="n"/>
+      <c r="B94" s="21" t="n"/>
+      <c r="C94" s="21" t="n"/>
+      <c r="D94" s="21" t="n"/>
+      <c r="E94" s="22" t="inlineStr">
+        <is>
+          <t>HT0642</t>
+        </is>
+      </c>
+      <c r="F94" s="23" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="G94" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="I94" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K94" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="M94" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="27" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="O94" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q94" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R94" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="21" t="n"/>
+      <c r="B95" s="21" t="n"/>
+      <c r="C95" s="21" t="n"/>
+      <c r="D95" s="21" t="n"/>
+      <c r="E95" s="22" t="inlineStr">
+        <is>
+          <t>HT0711</t>
+        </is>
+      </c>
+      <c r="F95" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G95" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I95" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K95" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O95" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q95" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R95" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="21" t="n"/>
+      <c r="B96" s="21" t="n"/>
+      <c r="C96" s="21" t="n"/>
+      <c r="D96" s="21" t="n"/>
+      <c r="E96" s="22" t="inlineStr">
+        <is>
+          <t>HT0712</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G96" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I96" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K96" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O96" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P96" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q96" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R96" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="21" t="n"/>
+      <c r="B97" s="21" t="n"/>
+      <c r="C97" s="21" t="n"/>
+      <c r="D97" s="21" t="n"/>
+      <c r="E97" s="22" t="inlineStr">
+        <is>
+          <t>HT0713</t>
+        </is>
+      </c>
+      <c r="F97" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G97" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I97" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K97" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O97" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q97" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R97" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="n"/>
+      <c r="B98" s="21" t="n"/>
+      <c r="C98" s="21" t="n"/>
+      <c r="D98" s="21" t="n"/>
+      <c r="E98" s="22" t="inlineStr">
+        <is>
+          <t>HT0714</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G98" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I98" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K98" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O98" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q98" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R98" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="n"/>
+      <c r="B99" s="21" t="n"/>
+      <c r="C99" s="21" t="n"/>
+      <c r="D99" s="21" t="n"/>
+      <c r="E99" s="22" t="inlineStr">
+        <is>
+          <t>HT0715</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G99" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I99" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K99" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O99" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q99" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R99" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="n"/>
+      <c r="B100" s="21" t="n"/>
+      <c r="C100" s="21" t="n"/>
+      <c r="D100" s="21" t="n"/>
+      <c r="E100" s="22" t="inlineStr">
+        <is>
+          <t>HT0716</t>
+        </is>
+      </c>
+      <c r="F100" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G100" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I100" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K100" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O100" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q100" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R100" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="n"/>
+      <c r="B101" s="21" t="n"/>
+      <c r="C101" s="21" t="n"/>
+      <c r="D101" s="21" t="n"/>
+      <c r="E101" s="22" t="inlineStr">
+        <is>
+          <t>HT0721</t>
+        </is>
+      </c>
+      <c r="F101" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G101" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I101" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K101" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O101" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q101" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R101" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="21" t="n"/>
+      <c r="B102" s="21" t="n"/>
+      <c r="C102" s="21" t="n"/>
+      <c r="D102" s="21" t="n"/>
+      <c r="E102" s="22" t="inlineStr">
+        <is>
+          <t>HT0722</t>
+        </is>
+      </c>
+      <c r="F102" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G102" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I102" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K102" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O102" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q102" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R102" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="n"/>
+      <c r="B103" s="21" t="n"/>
+      <c r="C103" s="21" t="n"/>
+      <c r="D103" s="21" t="n"/>
+      <c r="E103" s="22" t="inlineStr">
+        <is>
+          <t>HT0723</t>
+        </is>
+      </c>
+      <c r="F103" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G103" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I103" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K103" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O103" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q103" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R103" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="n"/>
+      <c r="B104" s="21" t="n"/>
+      <c r="C104" s="21" t="n"/>
+      <c r="D104" s="21" t="n"/>
+      <c r="E104" s="22" t="inlineStr">
+        <is>
+          <t>HT0731</t>
+        </is>
+      </c>
+      <c r="F104" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G104" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I104" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K104" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O104" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q104" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R104" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="21" t="n"/>
+      <c r="B105" s="21" t="n"/>
+      <c r="C105" s="21" t="n"/>
+      <c r="D105" s="21" t="n"/>
+      <c r="E105" s="22" t="inlineStr">
+        <is>
+          <t>HT0732</t>
+        </is>
+      </c>
+      <c r="F105" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G105" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I105" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K105" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O105" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q105" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R105" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="21" t="n"/>
+      <c r="B106" s="21" t="n"/>
+      <c r="C106" s="21" t="n"/>
+      <c r="D106" s="21" t="n"/>
+      <c r="E106" s="22" t="inlineStr">
+        <is>
+          <t>HT0733</t>
+        </is>
+      </c>
+      <c r="F106" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G106" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I106" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K106" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O106" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q106" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R106" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="21" t="n"/>
+      <c r="B107" s="21" t="n"/>
+      <c r="C107" s="21" t="n"/>
+      <c r="D107" s="21" t="n"/>
+      <c r="E107" s="22" t="inlineStr">
+        <is>
+          <t>HT0741</t>
+        </is>
+      </c>
+      <c r="F107" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G107" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I107" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K107" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O107" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q107" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R107" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="21" t="n"/>
+      <c r="B108" s="21" t="n"/>
+      <c r="C108" s="21" t="n"/>
+      <c r="D108" s="21" t="n"/>
+      <c r="E108" s="22" t="inlineStr">
+        <is>
+          <t>HT0742</t>
+        </is>
+      </c>
+      <c r="F108" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G108" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I108" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K108" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O108" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q108" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R108" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="21" t="n"/>
+      <c r="B109" s="21" t="n"/>
+      <c r="C109" s="21" t="n"/>
+      <c r="D109" s="21" t="n"/>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>HT0743</t>
+        </is>
+      </c>
+      <c r="F109" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G109" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I109" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K109" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O109" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q109" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R109" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="21" t="n"/>
+      <c r="B110" s="21" t="n"/>
+      <c r="C110" s="21" t="n"/>
+      <c r="D110" s="21" t="n"/>
+      <c r="E110" s="22" t="inlineStr">
+        <is>
+          <t>HT0751</t>
+        </is>
+      </c>
+      <c r="F110" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G110" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I110" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K110" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O110" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q110" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R110" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="21" t="n"/>
+      <c r="B111" s="21" t="n"/>
+      <c r="C111" s="21" t="n"/>
+      <c r="D111" s="21" t="n"/>
+      <c r="E111" s="22" t="inlineStr">
+        <is>
+          <t>HT0752</t>
+        </is>
+      </c>
+      <c r="F111" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G111" s="23" t="n">
+        <v>298</v>
+      </c>
+      <c r="H111" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I111" s="24" t="n">
+        <v>217</v>
+      </c>
+      <c r="J111" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K111" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="L111" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O111" s="27" t="n">
+        <v>230</v>
+      </c>
+      <c r="P111" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q111" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R111" s="35" t="n">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="21" t="n"/>
+      <c r="B112" s="21" t="n"/>
+      <c r="C112" s="21" t="n"/>
+      <c r="D112" s="21" t="n"/>
+      <c r="E112" s="22" t="inlineStr">
+        <is>
+          <t>HT0753</t>
+        </is>
+      </c>
+      <c r="F112" s="23" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="G112" s="23" t="n">
+        <v>1653</v>
+      </c>
+      <c r="H112" s="24" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I112" s="24" t="n">
+        <v>1205</v>
+      </c>
+      <c r="J112" s="25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K112" s="25" t="n">
+        <v>74</v>
+      </c>
+      <c r="L112" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="27" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="O112" s="27" t="n">
+        <v>1279</v>
+      </c>
+      <c r="P112" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q112" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R112" s="35" t="n">
+        <v>2932</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="21" t="n"/>
+      <c r="B113" s="21" t="n"/>
+      <c r="C113" s="21" t="n"/>
+      <c r="D113" s="21" t="n"/>
+      <c r="E113" s="22" t="inlineStr">
+        <is>
+          <t>HT0811</t>
+        </is>
+      </c>
+      <c r="F113" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G113" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I113" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K113" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M113" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O113" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q113" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R113" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="21" t="n"/>
+      <c r="B114" s="21" t="n"/>
+      <c r="C114" s="21" t="n"/>
+      <c r="D114" s="21" t="n"/>
+      <c r="E114" s="22" t="inlineStr">
+        <is>
+          <t>HT0812</t>
+        </is>
+      </c>
+      <c r="F114" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G114" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I114" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K114" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M114" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O114" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q114" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R114" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="21" t="n"/>
+      <c r="B115" s="21" t="n"/>
+      <c r="C115" s="21" t="n"/>
+      <c r="D115" s="21" t="n"/>
+      <c r="E115" s="22" t="inlineStr">
+        <is>
+          <t>HT0813</t>
+        </is>
+      </c>
+      <c r="F115" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G115" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I115" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K115" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M115" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O115" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q115" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R115" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="21" t="n"/>
+      <c r="B116" s="21" t="n"/>
+      <c r="C116" s="21" t="n"/>
+      <c r="D116" s="21" t="n"/>
+      <c r="E116" s="22" t="inlineStr">
+        <is>
+          <t>HT0814</t>
+        </is>
+      </c>
+      <c r="F116" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G116" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I116" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K116" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M116" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O116" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q116" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R116" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="21" t="n"/>
+      <c r="B117" s="21" t="n"/>
+      <c r="C117" s="21" t="n"/>
+      <c r="D117" s="21" t="n"/>
+      <c r="E117" s="22" t="inlineStr">
+        <is>
+          <t>HT0815</t>
+        </is>
+      </c>
+      <c r="F117" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G117" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I117" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K117" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M117" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O117" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q117" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R117" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="21" t="n"/>
+      <c r="B118" s="21" t="n"/>
+      <c r="C118" s="21" t="n"/>
+      <c r="D118" s="21" t="n"/>
+      <c r="E118" s="22" t="inlineStr">
+        <is>
+          <t>HT0821</t>
+        </is>
+      </c>
+      <c r="F118" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G118" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I118" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K118" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M118" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O118" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P118" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q118" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R118" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="21" t="n"/>
+      <c r="B119" s="21" t="n"/>
+      <c r="C119" s="21" t="n"/>
+      <c r="D119" s="21" t="n"/>
+      <c r="E119" s="22" t="inlineStr">
+        <is>
+          <t>HT0822</t>
+        </is>
+      </c>
+      <c r="F119" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G119" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I119" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K119" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M119" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O119" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q119" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R119" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="21" t="n"/>
+      <c r="B120" s="21" t="n"/>
+      <c r="C120" s="21" t="n"/>
+      <c r="D120" s="21" t="n"/>
+      <c r="E120" s="22" t="inlineStr">
+        <is>
+          <t>HT0823</t>
+        </is>
+      </c>
+      <c r="F120" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G120" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I120" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K120" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M120" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O120" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P120" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q120" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R120" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="21" t="n"/>
+      <c r="B121" s="21" t="n"/>
+      <c r="C121" s="21" t="n"/>
+      <c r="D121" s="21" t="n"/>
+      <c r="E121" s="22" t="inlineStr">
+        <is>
+          <t>HT0831</t>
+        </is>
+      </c>
+      <c r="F121" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G121" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I121" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K121" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M121" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O121" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q121" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R121" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="21" t="n"/>
+      <c r="B122" s="21" t="n"/>
+      <c r="C122" s="21" t="n"/>
+      <c r="D122" s="21" t="n"/>
+      <c r="E122" s="22" t="inlineStr">
+        <is>
+          <t>HT0832</t>
+        </is>
+      </c>
+      <c r="F122" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G122" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I122" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K122" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M122" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O122" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q122" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R122" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="21" t="n"/>
+      <c r="B123" s="21" t="n"/>
+      <c r="C123" s="21" t="n"/>
+      <c r="D123" s="21" t="n"/>
+      <c r="E123" s="22" t="inlineStr">
+        <is>
+          <t>HT0833</t>
+        </is>
+      </c>
+      <c r="F123" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G123" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I123" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K123" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M123" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O123" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q123" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R123" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="21" t="n"/>
+      <c r="B124" s="21" t="n"/>
+      <c r="C124" s="21" t="n"/>
+      <c r="D124" s="21" t="n"/>
+      <c r="E124" s="22" t="inlineStr">
+        <is>
+          <t>HT0834</t>
+        </is>
+      </c>
+      <c r="F124" s="23" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G124" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="24" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="I124" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K124" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M124" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="O124" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q124" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R124" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="21" t="n"/>
+      <c r="B125" s="21" t="n"/>
+      <c r="C125" s="21" t="n"/>
+      <c r="D125" s="21" t="n"/>
+      <c r="E125" s="22" t="inlineStr">
+        <is>
+          <t>HT0911</t>
+        </is>
+      </c>
+      <c r="F125" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G125" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I125" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K125" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M125" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O125" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q125" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R125" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="21" t="n"/>
+      <c r="B126" s="21" t="n"/>
+      <c r="C126" s="21" t="n"/>
+      <c r="D126" s="21" t="n"/>
+      <c r="E126" s="22" t="inlineStr">
+        <is>
+          <t>HT0912</t>
+        </is>
+      </c>
+      <c r="F126" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G126" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I126" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K126" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M126" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O126" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q126" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R126" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="21" t="n"/>
+      <c r="B127" s="21" t="n"/>
+      <c r="C127" s="21" t="n"/>
+      <c r="D127" s="21" t="n"/>
+      <c r="E127" s="22" t="inlineStr">
+        <is>
+          <t>HT0913</t>
+        </is>
+      </c>
+      <c r="F127" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G127" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I127" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K127" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M127" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O127" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q127" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R127" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="21" t="n"/>
+      <c r="B128" s="21" t="n"/>
+      <c r="C128" s="21" t="n"/>
+      <c r="D128" s="21" t="n"/>
+      <c r="E128" s="22" t="inlineStr">
+        <is>
+          <t>HT0914</t>
+        </is>
+      </c>
+      <c r="F128" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G128" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I128" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K128" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M128" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O128" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q128" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R128" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="21" t="n"/>
+      <c r="B129" s="21" t="n"/>
+      <c r="C129" s="21" t="n"/>
+      <c r="D129" s="21" t="n"/>
+      <c r="E129" s="22" t="inlineStr">
+        <is>
+          <t>HT0921</t>
+        </is>
+      </c>
+      <c r="F129" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G129" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I129" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K129" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M129" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O129" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q129" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R129" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="21" t="n"/>
+      <c r="B130" s="21" t="n"/>
+      <c r="C130" s="21" t="n"/>
+      <c r="D130" s="21" t="n"/>
+      <c r="E130" s="22" t="inlineStr">
+        <is>
+          <t>HT0922</t>
+        </is>
+      </c>
+      <c r="F130" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G130" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I130" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K130" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M130" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O130" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q130" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R130" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="21" t="n"/>
+      <c r="B131" s="21" t="n"/>
+      <c r="C131" s="21" t="n"/>
+      <c r="D131" s="21" t="n"/>
+      <c r="E131" s="22" t="inlineStr">
+        <is>
+          <t>HT0931</t>
+        </is>
+      </c>
+      <c r="F131" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G131" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I131" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K131" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M131" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O131" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q131" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R131" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="21" t="n"/>
+      <c r="B132" s="21" t="n"/>
+      <c r="C132" s="21" t="n"/>
+      <c r="D132" s="21" t="n"/>
+      <c r="E132" s="22" t="inlineStr">
+        <is>
+          <t>HT0932</t>
+        </is>
+      </c>
+      <c r="F132" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G132" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I132" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K132" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M132" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O132" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q132" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R132" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="21" t="n"/>
+      <c r="B133" s="21" t="n"/>
+      <c r="C133" s="21" t="n"/>
+      <c r="D133" s="21" t="n"/>
+      <c r="E133" s="22" t="inlineStr">
+        <is>
+          <t>HT0933</t>
+        </is>
+      </c>
+      <c r="F133" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G133" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I133" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K133" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M133" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O133" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q133" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R133" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="21" t="n"/>
+      <c r="B134" s="21" t="n"/>
+      <c r="C134" s="21" t="n"/>
+      <c r="D134" s="21" t="n"/>
+      <c r="E134" s="22" t="inlineStr">
+        <is>
+          <t>HT0934</t>
+        </is>
+      </c>
+      <c r="F134" s="23" t="n">
+        <v>47</v>
+      </c>
+      <c r="G134" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="24" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="I134" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K134" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="M134" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="27" t="n">
+        <v>53</v>
+      </c>
+      <c r="O134" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Q134" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R134" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="21" t="n"/>
+      <c r="B135" s="21" t="n"/>
+      <c r="C135" s="21" t="n"/>
+      <c r="D135" s="21" t="n"/>
+      <c r="E135" s="22" t="inlineStr">
+        <is>
+          <t>HT1011</t>
+        </is>
+      </c>
+      <c r="F135" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G135" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I135" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M135" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O135" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q135" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R135" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="21" t="n"/>
+      <c r="B136" s="21" t="n"/>
+      <c r="C136" s="21" t="n"/>
+      <c r="D136" s="21" t="n"/>
+      <c r="E136" s="22" t="inlineStr">
+        <is>
+          <t>HT1012</t>
+        </is>
+      </c>
+      <c r="F136" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G136" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I136" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M136" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O136" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q136" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R136" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="21" t="n"/>
+      <c r="B137" s="21" t="n"/>
+      <c r="C137" s="21" t="n"/>
+      <c r="D137" s="21" t="n"/>
+      <c r="E137" s="22" t="inlineStr">
+        <is>
+          <t>HT1013</t>
+        </is>
+      </c>
+      <c r="F137" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G137" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I137" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M137" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O137" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q137" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R137" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="21" t="n"/>
+      <c r="B138" s="21" t="n"/>
+      <c r="C138" s="21" t="n"/>
+      <c r="D138" s="21" t="n"/>
+      <c r="E138" s="22" t="inlineStr">
+        <is>
+          <t>HT1014</t>
+        </is>
+      </c>
+      <c r="F138" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G138" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I138" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M138" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O138" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q138" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R138" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="21" t="n"/>
+      <c r="B139" s="21" t="n"/>
+      <c r="C139" s="21" t="n"/>
+      <c r="D139" s="21" t="n"/>
+      <c r="E139" s="22" t="inlineStr">
+        <is>
+          <t>HT1021</t>
+        </is>
+      </c>
+      <c r="F139" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G139" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I139" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M139" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O139" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q139" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R139" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="21" t="n"/>
+      <c r="B140" s="21" t="n"/>
+      <c r="C140" s="21" t="n"/>
+      <c r="D140" s="21" t="n"/>
+      <c r="E140" s="22" t="inlineStr">
+        <is>
+          <t>HT1022</t>
+        </is>
+      </c>
+      <c r="F140" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G140" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I140" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M140" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O140" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q140" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R140" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="21" t="n"/>
+      <c r="B141" s="21" t="n"/>
+      <c r="C141" s="21" t="n"/>
+      <c r="D141" s="21" t="n"/>
+      <c r="E141" s="22" t="inlineStr">
+        <is>
+          <t>HT1023</t>
+        </is>
+      </c>
+      <c r="F141" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G141" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I141" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M141" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O141" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q141" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R141" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="21" t="n"/>
+      <c r="B142" s="21" t="n"/>
+      <c r="C142" s="21" t="n"/>
+      <c r="D142" s="21" t="n"/>
+      <c r="E142" s="22" t="inlineStr">
+        <is>
+          <t>HT1024</t>
+        </is>
+      </c>
+      <c r="F142" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G142" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I142" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K142" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M142" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O142" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q142" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R142" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="21" t="n"/>
+      <c r="B143" s="21" t="n"/>
+      <c r="C143" s="21" t="n"/>
+      <c r="D143" s="21" t="n"/>
+      <c r="E143" s="22" t="inlineStr">
+        <is>
+          <t>HT1025</t>
+        </is>
+      </c>
+      <c r="F143" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G143" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I143" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K143" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M143" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O143" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q143" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R143" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="21" t="n"/>
+      <c r="B144" s="21" t="n"/>
+      <c r="C144" s="21" t="n"/>
+      <c r="D144" s="21" t="n"/>
+      <c r="E144" s="22" t="inlineStr">
+        <is>
+          <t>HT1031</t>
+        </is>
+      </c>
+      <c r="F144" s="23" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G144" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="I144" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K144" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" s="26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M144" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="27" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O144" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="27" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q144" s="22" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R144" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="21" t="n"/>
+      <c r="B145" s="21" t="n"/>
+      <c r="C145" s="21" t="n"/>
+      <c r="D145" s="21" t="n"/>
+      <c r="E145" s="29" t="inlineStr">
+        <is>
+          <t>HT1032</t>
+        </is>
+      </c>
+      <c r="F145" s="30" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="G145" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="I145" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" s="33" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M145" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="34" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O145" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="34" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="Q145" s="29" t="inlineStr">
+        <is>
+          <t>Retourné</t>
+        </is>
+      </c>
+      <c r="R145" s="35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E1:R1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -23456,7 +31198,7 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>21/10/2025 16:11</t>
+          <t>21/10/2025 16:18</t>
         </is>
       </c>
     </row>
